--- a/public/form/出貨明細_範本.xlsx
+++ b/public/form/出貨明細_範本.xlsx
@@ -96,14 +96,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
@@ -111,7 +111,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
@@ -458,7 +458,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="28.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.375" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.125" style="2" customWidth="1"/>
@@ -470,7 +470,7 @@
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -482,7 +482,7 @@
       <c r="F1" s="4"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -493,7 +493,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -504,7 +504,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:8" s="9" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="9" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>

--- a/public/form/出貨明細_範本.xlsx
+++ b/public/form/出貨明細_範本.xlsx
@@ -24,11 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>商品類別</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,10 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>備註</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>出貨單號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,6 +63,82 @@
   </si>
   <si>
     <t>核准日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROD_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2公分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.5公分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2公分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>內容置左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>置中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>置中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已下有內容才畫格線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已下有內容才畫格線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO_SHOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP_USER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OUT_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INPUT_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP_DATE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -132,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -140,19 +208,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -175,6 +255,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,77 +558,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="28.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="35.125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="7.5" style="9" customWidth="1"/>
-    <col min="6" max="6" width="18.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="35.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="8" customWidth="1"/>
+    <col min="5" max="5" width="1.5" style="12" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.125" style="4" customWidth="1"/>
+    <col min="8" max="9" width="7.5" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="H1" s="6"/>
+      <c r="G2" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="G3" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:9" s="8" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" s="9" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>5</v>
-      </c>
+    <row r="6" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="D6" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="I6" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.59055118110236227" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"微軟正黑體,粗體"&amp;16總部出貨單明細</oddHeader>
   </headerFooter>

--- a/public/form/出貨明細_範本.xlsx
+++ b/public/form/出貨明細_範本.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>商品類別</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,82 +63,6 @@
   </si>
   <si>
     <t>核准日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PROD_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2公分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.5公分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2公分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>內容置左</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>置中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>置中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已下有內容才畫格線</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已下有內容才畫格線</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO_SHOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>APP_USER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>USER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OUT_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INPUT_DATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>APP_DATE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -200,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -208,28 +132,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -267,15 +176,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
@@ -576,16 +476,10 @@
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D1" s="3"/>
       <c r="E1" s="9"/>
       <c r="F1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="H1" s="5"/>
     </row>
@@ -593,33 +487,21 @@
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D2" s="6"/>
       <c r="E2" s="10"/>
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="3" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D3" s="6"/>
       <c r="E3" s="10"/>
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="4" spans="1:9" s="8" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -647,104 +529,6 @@
       <c r="I4" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="D6" s="14">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E6" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="I6" s="14">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/public/form/出貨明細_範本.xlsx
+++ b/public/form/出貨明細_範本.xlsx
@@ -70,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -87,14 +87,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
@@ -105,6 +97,21 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -138,45 +145,51 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,72 +474,86 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="20.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="35.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="1.5" style="12" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="1.5" style="6" customWidth="1"/>
     <col min="6" max="6" width="20.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.125" style="4" customWidth="1"/>
-    <col min="8" max="9" width="7.5" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="7" max="7" width="35.125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="7.5" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="2" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="2" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="2" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" s="8" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:9" s="4" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
